--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.50443</v>
+        <v>16.99898</v>
       </c>
       <c r="D2" t="n">
-        <v>16.61644</v>
+        <v>16.46233</v>
       </c>
       <c r="E2" t="n">
-        <v>16.8452</v>
+        <v>16.75844</v>
       </c>
       <c r="F2" t="n">
-        <v>42.73236</v>
+        <v>42.22128</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05075</v>
+        <v>0.05068</v>
       </c>
       <c r="H2" t="n">
-        <v>1.833</v>
+        <v>1.81816</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.8199</v>
+        <v>16.9623</v>
       </c>
       <c r="D3" t="n">
-        <v>16.76865</v>
+        <v>16.48626</v>
       </c>
       <c r="E3" t="n">
-        <v>16.9298</v>
+        <v>16.62317</v>
       </c>
       <c r="F3" t="n">
-        <v>42.82775</v>
+        <v>42.0561</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05102</v>
+        <v>0.05151</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81129</v>
+        <v>1.8412</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.88083</v>
+        <v>16.9737</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6692</v>
+        <v>16.68123</v>
       </c>
       <c r="E4" t="n">
-        <v>16.94587</v>
+        <v>16.8229</v>
       </c>
       <c r="F4" t="n">
-        <v>41.71137</v>
+        <v>42.73334</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05018</v>
+        <v>0.05121</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85112</v>
+        <v>1.87133</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.93136</v>
+        <v>17.01836</v>
       </c>
       <c r="D6" t="n">
-        <v>15.85325</v>
+        <v>16.46032</v>
       </c>
       <c r="E6" t="n">
-        <v>16.30482</v>
+        <v>16.92116</v>
       </c>
       <c r="F6" t="n">
-        <v>21.73664</v>
+        <v>22.02458</v>
       </c>
       <c r="G6" t="n">
-        <v>34.3893</v>
+        <v>35.84958</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.21889</v>
+        <v>16.55856</v>
       </c>
       <c r="D7" t="n">
-        <v>16.49255</v>
+        <v>16.02999</v>
       </c>
       <c r="E7" t="n">
-        <v>16.61255</v>
+        <v>16.5579</v>
       </c>
       <c r="F7" t="n">
-        <v>21.82322</v>
+        <v>21.86782</v>
       </c>
       <c r="G7" t="n">
-        <v>33.56215</v>
+        <v>34.39267</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.40253</v>
+        <v>16.5842</v>
       </c>
       <c r="D8" t="n">
-        <v>16.23217</v>
+        <v>15.9134</v>
       </c>
       <c r="E8" t="n">
-        <v>16.54706</v>
+        <v>16.50002</v>
       </c>
       <c r="F8" t="n">
-        <v>21.38938</v>
+        <v>22.12812</v>
       </c>
       <c r="G8" t="n">
-        <v>34.53046</v>
+        <v>33.35915</v>
       </c>
     </row>
   </sheetData>
